--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>17597.56</v>
+        <v>17421.94</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2268.72</v>
+        <v>2244.96</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2773.32</v>
+        <v>2744.27</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4628.81</v>
+        <v>4644.04</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>744.3</v>
+        <v>749.46</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5710.29</v>
+        <v>5686.75</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3949.76</v>
+        <v>3941.22</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13429.67</v>
+        <v>13465.28</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41229.92</v>
+        <v>42232.53</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>54261.28</v>
+        <v>53855.19</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>62773.11</v>
+        <v>62945.44</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18936.06</v>
+        <v>19060.77</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11705.73</v>
+        <v>11688.5</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1322.34</v>
+        <v>1315.14</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23987.57</v>
+        <v>23846.21</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9530.67</v>
+        <v>9474.51</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1833.62</v>
+        <v>1826.54</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>991.46</v>
+        <v>996.59</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3048.67</v>
+        <v>3051.6</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4427.06</v>
+        <v>4622.57</v>
       </c>
     </row>
     <row r="22">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2196.01</v>
+        <v>2195.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3850-76-CM26</t>
+          <t>952946-40-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>913.75</v>
+        <v>1378.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>952946-40-CM26</t>
+          <t>1432083-423-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1377.06</v>
+        <v>1883.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1432083-423-CM26</t>
+          <t>3850-76-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1881.66</v>
+        <v>914.54</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1628.77</v>
+        <v>1624.27</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1334</v>
+        <v>1314.11</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1822.99</v>
+        <v>1812.52</v>
       </c>
     </row>
     <row r="29">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2122.45</v>
+        <v>2110.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057545-281-CM26</t>
+          <t>1432083-496-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2703.79</v>
+        <v>4856.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1432083-494-CM26</t>
+          <t>1057545-281-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1132.03</v>
+        <v>2686.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1432083-495-CM26</t>
+          <t>1432083-494-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1739.16</v>
+        <v>1124.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1432083-496-CM26</t>
+          <t>1432083-495-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4887.42</v>
+        <v>1728.01</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>913.75</v>
+        <v>894.09</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1788.54</v>
+        <v>1746.92</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>30490.55</v>
+        <v>29781.06</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2476.39</v>
+        <v>2431.48</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>13235.79</v>
+        <v>13274.32</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2987.38</v>
+        <v>3012.74</v>
       </c>
     </row>
     <row r="40">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2895.14</v>
+        <v>2930.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3334-154-CM26</t>
+          <t>4062-290-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3570.45</v>
+        <v>5064.59</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4062-290-CM26</t>
+          <t>3334-154-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.838.249-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5007.65</v>
+        <v>3611.06</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5072.3</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3514.1</v>
+        <v>3528.66</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1097.8</v>
+        <v>1102.35</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18373.46</v>
+        <v>18263.34</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1098.1</v>
+        <v>1083.17</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2543.76</v>
+        <v>2522.06</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3008.91</v>
+        <v>3025.12</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1021.85</v>
+        <v>1033.28</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3434.43</v>
+        <v>3447.44</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1000.9</v>
+        <v>1004.7</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1532.28</v>
+        <v>1546.84</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1423.3</v>
+        <v>1436.82</v>
       </c>
     </row>
     <row r="55">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22270.39</v>
+        <v>22436.31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1432083-1118-CM26</t>
+          <t>1432083-1082-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2568.84</v>
+        <v>2178.04</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1432083-1082-CM26</t>
+          <t>707424-35-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2201.99</v>
+        <v>1326.62</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>707424-35-CM26</t>
+          <t>1432083-1118-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1341.21</v>
+        <v>2540.9</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>860.78</v>
+        <v>858.65</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3955.3</v>
+        <v>3974.73</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2256.68</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2256.68</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4018.63</v>
+        <v>4031.96</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9778.879999999999</v>
+        <v>9811.32</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2201.99</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3271.33</v>
+        <v>3318.14</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1119.61</v>
+        <v>1135.63</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2281.44</v>
+        <v>2308.2</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1067.31</v>
+        <v>1079.83</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3585.08</v>
+        <v>3618.7</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5335.7</v>
+        <v>5262.38</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1112.48</v>
+        <v>1137.57</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1225.05</v>
+        <v>1221.81</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>22908.7</v>
+        <v>22603.55</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2062.25</v>
+        <v>2021.88</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2476.87</v>
+        <v>2486.54</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4109.28</v>
+        <v>4125.27</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>968.42</v>
+        <v>970.49</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4109.28</v>
+        <v>4118.7</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2081.79</v>
+        <v>2095.72</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>819.22</v>
+        <v>824.96</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>920.42</v>
+        <v>917.51</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1768.56</v>
+        <v>1765.01</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2324.34</v>
+        <v>2310.89</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2573.03</v>
+        <v>2558.13</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2292.62</v>
+        <v>2279.91</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,68 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1580.86</v>
+        <v>1591.44</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1432083-1920-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>1914.58</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5418-280-CM25</t>
+          <t>5657-84-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>17421.94</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1432083-1819-CM25</t>
+          <t>3335-407-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2244.96</v>
+        <v>1952.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2281-7784-CM25</t>
+          <t>707424-63-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2744.27</v>
+        <v>1332.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5538-438-CM25</t>
+          <t>1432083-1058-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.959.575-9</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4644.04</v>
+        <v>2232.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>707424-117-CM25</t>
+          <t>3335-1599-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>749.46</v>
+        <v>1567.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3334-3876-CM25</t>
+          <t>1432083-1467-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5686.75</v>
+        <v>932.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2905-1015-CM25</t>
+          <t>1079694-353-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3941.22</v>
+        <v>1013.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4062-1045-CM25</t>
+          <t>1432083-1599-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13465.28</v>
+        <v>1243.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079694-20-CM26</t>
+          <t>5418-280-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>42232.53</v>
+        <v>17421.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1340-42-CM26</t>
+          <t>1432083-1819-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BLOOMBERRY COMERCIAL SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.330.742-5</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>53855.19</v>
+        <v>2244.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3335-109-CM26</t>
+          <t>2281-7784-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>62945.44</v>
+        <v>2744.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1432083-84-CM26</t>
+          <t>5538-438-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.959.575-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19060.77</v>
+        <v>4644.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3141-41-CM26</t>
+          <t>707424-117-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11688.5</v>
+        <v>749.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5625-12-CM26</t>
+          <t>3334-3876-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.978.990-3</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>76.838.249-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1315.14</v>
+        <v>5686.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1432083-148-CM26</t>
+          <t>2905-1015-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23846.21</v>
+        <v>3941.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1432083-149-CM26</t>
+          <t>4062-1045-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9474.51</v>
+        <v>13465.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3335-124-CM26</t>
+          <t>1079694-20-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1826.54</v>
+        <v>42232.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1432083-187-CM26</t>
+          <t>1340-42-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.330.742-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>996.59</v>
+        <v>53855.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057545-188-CM26</t>
+          <t>3335-109-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3051.6</v>
+        <v>62945.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3568-189-CM26</t>
+          <t>1432083-84-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4622.57</v>
+        <v>19060.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>952946-36-CM26</t>
+          <t>3141-41-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2195.9</v>
+        <v>11688.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>952946-40-CM26</t>
+          <t>5625-12-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.978.990-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1378.24</v>
+        <v>1315.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1432083-423-CM26</t>
+          <t>1432083-149-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1883.28</v>
+        <v>9474.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3850-76-CM26</t>
+          <t>1432083-148-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>914.54</v>
+        <v>23846.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1432083-440-CM26</t>
+          <t>3335-124-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1624.27</v>
+        <v>1826.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1432083-448-CM26</t>
+          <t>1432083-187-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,17 +2049,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1314.11</v>
+        <v>996.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1218393-99-CM26</t>
+          <t>1057545-188-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1812.52</v>
+        <v>3051.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1218393-100-CM26</t>
+          <t>3568-189-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2110.26</v>
+        <v>4622.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1432083-496-CM26</t>
+          <t>952946-36-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4856.11</v>
+        <v>2195.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057545-281-CM26</t>
+          <t>952946-40-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2686.47</v>
+        <v>1378.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1432083-494-CM26</t>
+          <t>1432083-423-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1124.78</v>
+        <v>1883.28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1432083-495-CM26</t>
+          <t>3850-76-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1728.01</v>
+        <v>914.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3850-114-CM26</t>
+          <t>1432083-440-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>894.09</v>
+        <v>1624.27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3335-248-CM26</t>
+          <t>1432083-448-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1746.92</v>
+        <v>1314.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1079694-90-CM26</t>
+          <t>1218393-100-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>29781.06</v>
+        <v>2110.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1432083-578-CM26</t>
+          <t>1218393-99-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2431.48</v>
+        <v>1812.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3833-244-CM26</t>
+          <t>1432083-494-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>13274.32</v>
+        <v>1124.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>952946-61-CM26</t>
+          <t>1432083-495-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3012.74</v>
+        <v>1728.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1432083-691-CM26</t>
+          <t>1432083-496-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2930.77</v>
+        <v>4856.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4062-290-CM26</t>
+          <t>1057545-281-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5064.59</v>
+        <v>2686.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3334-154-CM26</t>
+          <t>3850-114-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3611.06</v>
+        <v>894.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1432083-796-CM26</t>
+          <t>3335-248-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5118</v>
+        <v>1746.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1432083-835-CM26</t>
+          <t>1079694-90-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3528.66</v>
+        <v>29781.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1432083-833-CM26</t>
+          <t>1432083-578-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1102.35</v>
+        <v>2431.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2905-291-CM26</t>
+          <t>3833-244-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18263.34</v>
+        <v>13274.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3850-182-CM26</t>
+          <t>952946-61-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1083.17</v>
+        <v>3012.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1432083-943-CM26</t>
+          <t>1432083-691-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2522.06</v>
+        <v>2930.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1432083-963-CM26</t>
+          <t>4062-290-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3025.12</v>
+        <v>5064.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1432083-976-CM26</t>
+          <t>3334-154-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.838.249-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1033.28</v>
+        <v>3611.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3335-474-CM26</t>
+          <t>1432083-796-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3447.44</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1432083-1001-CM26</t>
+          <t>1432083-833-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1004.7</v>
+        <v>1102.35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1432083-998-CM26</t>
+          <t>1432083-835-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1546.84</v>
+        <v>3528.66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057553-173-CM26</t>
+          <t>2905-291-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1436.82</v>
+        <v>18263.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3141-110-CM26</t>
+          <t>3850-182-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22436.31</v>
+        <v>1083.17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1432083-1082-CM26</t>
+          <t>1432083-943-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2178.04</v>
+        <v>2522.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>707424-35-CM26</t>
+          <t>1432083-963-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1326.62</v>
+        <v>3025.12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1432083-1118-CM26</t>
+          <t>1432083-976-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2540.9</v>
+        <v>1033.28</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1432083-1121-CM26</t>
+          <t>3335-474-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>858.65</v>
+        <v>3447.44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5657-144-CM26</t>
+          <t>1432083-1001-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3974.73</v>
+        <v>1004.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1432083-1137-CM26</t>
+          <t>1057553-173-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,22 +4128,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2264.17</v>
+        <v>1436.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1432083-1138-CM26</t>
+          <t>1432083-998-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2264.17</v>
+        <v>1546.84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1432083-1164-CM26</t>
+          <t>3141-110-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4031.96</v>
+        <v>22436.31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1432083-1167-CM26</t>
+          <t>1432083-1082-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9811.32</v>
+        <v>2178.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1432083-1184-CM26</t>
+          <t>707424-35-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2209</v>
+        <v>1326.62</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4062-391-CM26</t>
+          <t>1432083-1118-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3318.14</v>
+        <v>2540.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1432083-1196-CM26</t>
+          <t>1432083-1121-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1135.63</v>
+        <v>858.65</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1432083-1212-CM26</t>
+          <t>5657-144-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2308.2</v>
+        <v>3974.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1432083-1221-CM26</t>
+          <t>1432083-1137-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1079.83</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3334-258-CM26</t>
+          <t>1432083-1138-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3618.7</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1432083-1350-CM26</t>
+          <t>1432083-1164-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5262.38</v>
+        <v>4031.96</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1432083-1440-CM26</t>
+          <t>1432083-1167-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,17 +4794,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1137.57</v>
+        <v>9811.32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1432083-1458-CM26</t>
+          <t>1432083-1184-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1221.81</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1079694-197-CM26</t>
+          <t>1432083-1196-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>22603.55</v>
+        <v>1135.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5657-184-CM26</t>
+          <t>4062-391-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2021.88</v>
+        <v>3318.14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1432083-1505-CM26</t>
+          <t>1432083-1212-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,17 +5038,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2486.54</v>
+        <v>2308.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3334-298-CM26</t>
+          <t>1432083-1221-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5099,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4125.27</v>
+        <v>1079.83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1723-406-CM26</t>
+          <t>3334-258-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.838.249-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>970.49</v>
+        <v>3618.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3334-312-CM26</t>
+          <t>1432083-1350-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,27 +5221,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4118.7</v>
+        <v>5262.38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1432083-1608-CM26</t>
+          <t>1432083-1440-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,17 +5282,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2095.72</v>
+        <v>1137.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1432083-1637-CM26</t>
+          <t>1432083-1458-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,17 +5343,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>824.96</v>
+        <v>1221.81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1432083-1657-CM26</t>
+          <t>1079694-197-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>917.51</v>
+        <v>22603.55</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1432083-1670-CM26</t>
+          <t>5657-184-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1765.01</v>
+        <v>2021.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1432083-1682-CM26</t>
+          <t>1432083-1505-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2310.89</v>
+        <v>2486.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1432083-1689-CM26</t>
+          <t>3334-298-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2558.13</v>
+        <v>4125.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1432083-1810-CM26</t>
+          <t>1723-406-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,22 +5653,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2279.91</v>
+        <v>970.49</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1432083-1838-CM26</t>
+          <t>3334-312-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1591.44</v>
+        <v>4118.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1432083-1920-CM26</t>
+          <t>1432083-1608-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,6 +5815,494 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
+        <v>2095.72</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1432083-1637-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>824.96</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1432083-1657-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>917.51</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1432083-1670-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1765.01</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1432083-1682-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>2310.89</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1432083-1689-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>2558.13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1432083-1810-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>2279.91</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1432083-1838-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1591.44</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1432083-1920-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
         <v>1914.58</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3850-128-CM25</t>
+          <t>1079694-45-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>76.959.575-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>788.35</v>
+        <v>44353.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1079694-45-CM25</t>
+          <t>3850-128-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.959.575-9</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44353.35</v>
+        <v>788.35</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1067,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5657-87-CM25</t>
+          <t>5657-97-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1590.29</v>
+        <v>4447.49</v>
       </c>
     </row>
     <row r="12">
@@ -1250,7 +1250,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5657-97-CM25</t>
+          <t>5657-87-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4447.49</v>
+        <v>1590.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5538-161-CM25</t>
+          <t>3335-407-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3388.09</v>
+        <v>1952.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3335-407-CM25</t>
+          <t>5538-161-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1952.94</v>
+        <v>3388.09</v>
       </c>
     </row>
     <row r="17">
@@ -1799,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057553-1624-CM25</t>
+          <t>1057553-1623-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1290.82</v>
+        <v>893.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057553-1623-CM25</t>
+          <t>1057553-1624-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>893.4</v>
+        <v>1290.82</v>
       </c>
     </row>
     <row r="25">
@@ -1982,7 +1982,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3334-3363-CM25</t>
+          <t>3334-3362-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2827.52</v>
+        <v>3393.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3334-3362-CM25</t>
+          <t>3334-3363-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3393.02</v>
+        <v>2827.52</v>
       </c>
     </row>
     <row r="28">
@@ -3080,7 +3080,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3335-1089-CM25</t>
+          <t>3334-3517-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.838.249-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1404.19</v>
+        <v>3362.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3334-3517-CM25</t>
+          <t>3335-1089-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3362.56</v>
+        <v>1404.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>707424-62-CM25</t>
+          <t>707424-63-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>RSB</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.369.114-4</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>730.41</v>
+        <v>1332.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>707424-63-CM25</t>
+          <t>707424-62-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>RSB</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>76.369.114-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1332.77</v>
+        <v>730.41</v>
       </c>
     </row>
     <row r="48">
@@ -4361,7 +4361,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1432083-1304-CM25</t>
+          <t>1432083-1361-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1032.81</v>
+        <v>926.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1432083-1361-CM25</t>
+          <t>1432083-1304-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>926.29</v>
+        <v>1032.81</v>
       </c>
     </row>
     <row r="67">
@@ -4544,7 +4544,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1432083-1454-CM25</t>
+          <t>2905-806-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1387.88</v>
+        <v>7060.35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2905-806-CM25</t>
+          <t>1432083-1454-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>7060.35</v>
+        <v>1387.88</v>
       </c>
     </row>
     <row r="70">
@@ -5032,7 +5032,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3143-148-CM25</t>
+          <t>1432083-1671-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>13804.46</v>
+        <v>1154.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1432083-1671-CM25</t>
+          <t>3143-148-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1154.12</v>
+        <v>13804.46</v>
       </c>
     </row>
     <row r="78">
@@ -5459,7 +5459,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1432083-1819-CM25</t>
+          <t>2281-7784-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5479,17 +5479,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2244.96</v>
+        <v>2744.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2281-7784-CM25</t>
+          <t>1432083-1819-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2744.27</v>
+        <v>2244.96</v>
       </c>
     </row>
     <row r="85">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6679,7 +6679,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3850-76-CM26</t>
+          <t>952946-40-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6699,17 +6699,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>914.54</v>
+        <v>1378.24</v>
       </c>
     </row>
     <row r="104">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6801,7 +6801,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>952946-40-CM26</t>
+          <t>3850-76-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6821,17 +6821,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1378.24</v>
+        <v>914.54</v>
       </c>
     </row>
     <row r="106">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7106,7 +7106,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1432083-494-CM26</t>
+          <t>1057545-281-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1124.78</v>
+        <v>2686.47</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1432083-495-CM26</t>
+          <t>1432083-496-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1728.01</v>
+        <v>4856.11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1432083-496-CM26</t>
+          <t>1432083-494-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4856.11</v>
+        <v>1124.78</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1057545-281-CM26</t>
+          <t>1432083-495-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7309,17 +7309,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2686.47</v>
+        <v>1728.01</v>
       </c>
     </row>
     <row r="114">
@@ -7411,7 +7411,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1079694-90-CM26</t>
+          <t>3335-248-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7431,17 +7431,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>29781.06</v>
+        <v>1746.92</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3335-248-CM26</t>
+          <t>1079694-90-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1746.92</v>
+        <v>29781.06</v>
       </c>
     </row>
     <row r="117">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8692,7 +8692,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>707424-35-CM26</t>
+          <t>1432083-1118-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1326.62</v>
+        <v>2540.9</v>
       </c>
     </row>
     <row r="137">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8814,7 +8814,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1432083-1118-CM26</t>
+          <t>707424-35-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2540.9</v>
+        <v>1326.62</v>
       </c>
     </row>
     <row r="139">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1432083-1212-CM26</t>
+          <t>1432083-1221-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2308.2</v>
+        <v>1079.83</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1432083-1221-CM26</t>
+          <t>1432083-1212-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1079.83</v>
+        <v>2308.2</v>
       </c>
     </row>
     <row r="150">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11737,6 +11737,799 @@
       </c>
       <c r="M185" s="2" t="n">
         <v>4659.87</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2905-593-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>2263.58</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2905-594-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>5955.59</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1432083-2175-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>4237.89</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1432083-2128-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>4696.94</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1432083-2191-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>3845.97</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2905-642-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>5268</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>952946-182-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>1532.04</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>5657-268-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>3859.17</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1432083-2373-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>3371.97</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1432083-2354-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>2680.18</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>3545-262-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>65.273.020-5</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>1897.66</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1432083-2204-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>1856.11</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1723-591-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>4057.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +753,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1367,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1676,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1741,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1806,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1932,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +2973,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4075,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4323,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4632,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5185,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5494,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5742,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +5868,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +5933,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6120,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6246,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6616,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6742,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7112,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7726,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +7974,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8222,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8409,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +8779,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9149,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9214,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9340,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9527,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +9958,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10206,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10576,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11007,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11072,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11320,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11446,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11572,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +11881,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12007,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12072,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12259,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12385,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12633,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +12698,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -5002,7 +5002,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7604,7 +7608,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M198"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079694-45-CM25</t>
+          <t>3850-128-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,28 +684,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.959.575-9</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>77.823.479-3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44353.35</v>
+        <v>788.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3850-128-CM25</t>
+          <t>1079694-45-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -725,17 +729,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,26 +749,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.959.575-9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>788.35</v>
+        <v>44353.35</v>
       </c>
     </row>
     <row r="6">
@@ -1075,7 +1075,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5657-97-CM25</t>
+          <t>5657-87-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4447.49</v>
+        <v>1590.29</v>
       </c>
     </row>
     <row r="12">
@@ -1258,7 +1258,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5657-87-CM25</t>
+          <t>5657-97-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1590.29</v>
+        <v>4447.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3335-407-CM25</t>
+          <t>5538-161-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1359,32 +1359,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>83.610.800-0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1952.94</v>
+        <v>3388.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5538-161-CM25</t>
+          <t>3335-407-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1404,17 +1400,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1424,22 +1420,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3388.09</v>
+        <v>1952.94</v>
       </c>
     </row>
     <row r="17">
@@ -1823,7 +1823,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057553-1623-CM25</t>
+          <t>1057553-1624-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1863,28 +1863,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>893.4</v>
+        <v>1290.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057553-1624-CM25</t>
+          <t>1057553-1623-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1924,26 +1928,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1290.82</v>
+        <v>893.4</v>
       </c>
     </row>
     <row r="25">
@@ -2010,7 +2010,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3334-3362-CM25</t>
+          <t>3334-3363-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3393.02</v>
+        <v>2827.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3334-3363-CM25</t>
+          <t>3334-3362-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2827.52</v>
+        <v>3393.02</v>
       </c>
     </row>
     <row r="28">
@@ -3112,7 +3112,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3334-3517-CM25</t>
+          <t>3335-1089-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3167,13 +3167,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3362.56</v>
+        <v>1404.19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3335-1089-CM25</t>
+          <t>3334-3517-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.838.249-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3228,13 +3228,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1404.19</v>
+        <v>3362.56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>707424-63-CM25</t>
+          <t>707424-62-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>RSB</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>76.369.114-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3289,13 +3289,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1332.77</v>
+        <v>730.41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>707424-62-CM25</t>
+          <t>707424-63-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RSB</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.369.114-4</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>730.41</v>
+        <v>1332.77</v>
       </c>
     </row>
     <row r="48">
@@ -4401,7 +4401,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1432083-1361-CM25</t>
+          <t>1432083-1304-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4456,13 +4456,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>926.29</v>
+        <v>1032.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1432083-1304-CM25</t>
+          <t>1432083-1361-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1032.81</v>
+        <v>926.29</v>
       </c>
     </row>
     <row r="67">
@@ -4584,7 +4584,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2905-806-CM25</t>
+          <t>1432083-1454-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4624,32 +4624,28 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7060.35</v>
+        <v>1387.88</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1432083-1454-CM25</t>
+          <t>2905-806-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4674,12 +4670,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4689,22 +4685,26 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1387.88</v>
+        <v>7060.35</v>
       </c>
     </row>
     <row r="70">
@@ -5080,7 +5080,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1432083-1671-CM25</t>
+          <t>3143-148-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5120,28 +5120,32 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>77.819.582-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1154.12</v>
+        <v>13804.46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3143-148-CM25</t>
+          <t>1432083-1671-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5166,12 +5170,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5181,26 +5185,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13804.46</v>
+        <v>1154.12</v>
       </c>
     </row>
     <row r="78">
@@ -5515,7 +5515,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2281-7784-CM25</t>
+          <t>1432083-1819-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5535,17 +5535,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2744.27</v>
+        <v>2244.96</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1432083-1819-CM25</t>
+          <t>2281-7784-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2244.96</v>
+        <v>2744.27</v>
       </c>
     </row>
     <row r="85">
@@ -6763,7 +6763,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>952946-40-CM26</t>
+          <t>3850-76-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6783,17 +6783,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1378.24</v>
+        <v>914.54</v>
       </c>
     </row>
     <row r="104">
@@ -6885,7 +6885,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3850-76-CM26</t>
+          <t>952946-40-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6905,17 +6905,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>914.54</v>
+        <v>1378.24</v>
       </c>
     </row>
     <row r="106">
@@ -7068,7 +7068,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1218393-99-CM26</t>
+          <t>1218393-100-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7108,32 +7108,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1812.52</v>
+        <v>2110.26</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1218393-100-CM26</t>
+          <t>1218393-99-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7173,22 +7169,26 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2110.26</v>
+        <v>1812.52</v>
       </c>
     </row>
     <row r="110">
@@ -7316,7 +7316,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1432083-494-CM26</t>
+          <t>1432083-495-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7371,13 +7371,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1124.78</v>
+        <v>1728.01</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1432083-495-CM26</t>
+          <t>1432083-494-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1728.01</v>
+        <v>1124.78</v>
       </c>
     </row>
     <row r="114">
@@ -7499,7 +7499,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3335-248-CM26</t>
+          <t>1079694-90-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7519,17 +7519,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7539,28 +7539,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1746.92</v>
+        <v>29781.06</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1079694-90-CM26</t>
+          <t>3335-248-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7580,17 +7584,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7600,26 +7604,22 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>29781.06</v>
+        <v>1746.92</v>
       </c>
     </row>
     <row r="117">
@@ -7873,7 +7873,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3334-154-CM26</t>
+          <t>4062-290-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7893,17 +7893,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7913,28 +7913,32 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PELLET ENERGY SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.838.249-2</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3611.06</v>
+        <v>5064.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4062-290-CM26</t>
+          <t>3334-154-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7954,17 +7958,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7974,26 +7978,22 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>PELLET ENERGY SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.838.249-2</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5064.59</v>
+        <v>3611.06</v>
       </c>
     </row>
     <row r="123">
@@ -8495,7 +8495,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3335-474-CM26</t>
+          <t>1432083-1001-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8515,17 +8515,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8550,13 +8550,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3447.44</v>
+        <v>1004.7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1432083-1001-CM26</t>
+          <t>3335-474-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8576,17 +8576,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1004.7</v>
+        <v>3447.44</v>
       </c>
     </row>
     <row r="133">
@@ -8804,7 +8804,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1432083-1118-CM26</t>
+          <t>1432083-1082-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8859,13 +8859,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2540.9</v>
+        <v>2178.04</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1432083-1082-CM26</t>
+          <t>707424-35-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8920,13 +8920,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2178.04</v>
+        <v>1326.62</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>707424-35-CM26</t>
+          <t>1432083-1118-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1326.62</v>
+        <v>2540.9</v>
       </c>
     </row>
     <row r="139">
@@ -9109,7 +9109,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1432083-1137-CM26</t>
+          <t>1432083-1138-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9174,7 +9174,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1432083-1138-CM26</t>
+          <t>1432083-1164-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9214,32 +9214,28 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2264.17</v>
+        <v>4031.96</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1432083-1164-CM26</t>
+          <t>1432083-1167-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9279,28 +9275,32 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4031.96</v>
+        <v>9811.32</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1432083-1167-CM26</t>
+          <t>1432083-1137-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>9811.32</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="145">
@@ -10536,7 +10536,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1432083-1682-CM26</t>
+          <t>1432083-1689-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10576,32 +10576,28 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2310.89</v>
+        <v>2558.13</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1432083-1689-CM26</t>
+          <t>1432083-1682-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10641,22 +10637,26 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2558.13</v>
+        <v>2310.89</v>
       </c>
     </row>
     <row r="166">
@@ -10967,7 +10967,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3335-936-CM26</t>
+          <t>1079694-260-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11026,13 +11026,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3462.12</v>
+        <v>2896.66</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1079694-260-CM26</t>
+          <t>3335-936-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11052,17 +11052,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2896.66</v>
+        <v>3462.12</v>
       </c>
     </row>
     <row r="173">
@@ -11471,7 +11471,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1432083-2078-CM26</t>
+          <t>1057553-309-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11511,28 +11511,32 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3061.21</v>
+        <v>1240.17</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1057553-309-CM26</t>
+          <t>1432083-2078-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11557,12 +11561,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11572,26 +11576,22 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1240.17</v>
+        <v>3061.21</v>
       </c>
     </row>
     <row r="181">
@@ -11658,7 +11658,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1432083-2086-CM26</t>
+          <t>707424-66-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11713,13 +11713,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1076.12</v>
+        <v>2153.29</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>707424-66-CM26</t>
+          <t>1432083-2086-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11774,7 +11774,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2153.29</v>
+        <v>1076.12</v>
       </c>
     </row>
     <row r="184">
@@ -11967,7 +11967,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2905-594-CM26</t>
+          <t>1432083-2175-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12007,17 +12007,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5955.59</v>
+        <v>4237.89</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1432083-2175-CM26</t>
+          <t>1432083-2191-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12072,26 +12072,22 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4237.89</v>
+        <v>3845.97</v>
       </c>
     </row>
     <row r="189">
@@ -12158,7 +12154,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1432083-2191-CM26</t>
+          <t>2905-642-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12173,7 +12169,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12183,12 +12179,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12198,28 +12194,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3845.97</v>
+        <v>5268</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2905-642-CM26</t>
+          <t>952946-182-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12234,22 +12234,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12259,32 +12259,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5268</v>
+        <v>1532.04</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>952946-182-CM26</t>
+          <t>5657-268-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12299,22 +12295,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12324,28 +12320,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1532.04</v>
+        <v>3859.17</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5657-268-CM26</t>
+          <t>5657-262-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -12385,26 +12385,22 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.756.768-5</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3859.17</v>
+        <v>6046.81</v>
       </c>
     </row>
     <row r="194">
@@ -12532,7 +12528,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3545-262-CM26</t>
+          <t>1432083-2204-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12552,17 +12548,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>65.273.020-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12572,28 +12568,32 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1897.66</v>
+        <v>1856.11</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1432083-2204-CM26</t>
+          <t>3545-262-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12613,17 +12613,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>65.273.020-5</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12633,26 +12633,22 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1856.11</v>
+        <v>1897.66</v>
       </c>
     </row>
     <row r="198">
@@ -12718,6 +12714,693 @@
       </c>
       <c r="M198" s="2" t="n">
         <v>4057.29</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1432083-2438-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>2784.76</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1432083-2486-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>3470.01</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1057552-972-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.607.508-K</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>MARYUN Seguridad Industrial</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>955.21</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1432083-2434-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>1204.17</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1495209-25-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>3107.19</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>3334-485-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>ELECTROCOM S A</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>96.355.000-6</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>1824.02</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>3334-484-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>ELECTROCOM S A</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>96.355.000-6</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>5836.85</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1495209-24-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>1323.23</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1495209-21-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>3411.61</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>4062-739-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>69.200.400-0</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>11728.63</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1495209-27-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>5511.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-rios.xlsx
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
